--- a/DataTables/Datas/#Chapter_Mission.xlsx
+++ b/DataTables/Datas/#Chapter_Mission.xlsx
@@ -1102,7 +1102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:5">
       <c r="B5">
         <v>1001001</v>
       </c>
@@ -1113,10 +1113,10 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="B6">
         <v>1001002</v>
       </c>
@@ -1127,10 +1127,10 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="B7">
         <v>1001003</v>
       </c>
@@ -1141,10 +1141,10 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="B8">
         <v>1001004</v>
       </c>
@@ -1155,10 +1155,10 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="B9">
         <v>1001005</v>
       </c>
@@ -1169,10 +1169,10 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="B10">
         <v>1001006</v>
       </c>
@@ -1183,10 +1183,10 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="B11">
         <v>1001007</v>
       </c>
@@ -1197,10 +1197,10 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="B12">
         <v>1001008</v>
       </c>
@@ -1211,10 +1211,10 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="B13">
         <v>1001009</v>
       </c>
@@ -1225,10 +1225,10 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="B14">
         <v>1001010</v>
       </c>
@@ -1239,10 +1239,10 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="B15">
         <v>1001011</v>
       </c>
@@ -1253,10 +1253,10 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="B16">
         <v>1001012</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -1281,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -1295,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -1323,7 +1323,7 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -1337,7 +1337,7 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="2:5">
@@ -1351,7 +1351,7 @@
         <v>1</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="2:5">
@@ -1365,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="2:5">
@@ -1379,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
